--- a/output/2026年4月/党费收缴子表/2026年4月-2026年计算机科学与技术学院研究生第二党支部-党费收缴子表.xlsx
+++ b/output/2026年4月/党费收缴子表/2026年4月-2026年计算机科学与技术学院研究生第二党支部-党费收缴子表.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O47"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -583,7 +583,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>姓 名</t>
+          <t>撒海萍</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
@@ -628,11 +628,11 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>撒海萍</t>
+          <t>王琳影</t>
         </is>
       </c>
       <c r="C5" s="6" t="n">
@@ -677,11 +677,11 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>王琳影</t>
+          <t>万榕</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
@@ -726,11 +726,11 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>万榕</t>
+          <t>罗倩</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
@@ -775,11 +775,11 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>罗倩</t>
+          <t>贾理淦</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
@@ -824,11 +824,11 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>贾理淦</t>
+          <t>冯志魁</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
@@ -873,11 +873,11 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>冯志魁</t>
+          <t>程凯</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
@@ -922,11 +922,11 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>程凯</t>
+          <t>刁琳双</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
@@ -971,11 +971,11 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>刁琳双</t>
+          <t>贺斯佳</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
@@ -1020,11 +1020,11 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>贺斯佳</t>
+          <t>杨广恒</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
@@ -1069,11 +1069,11 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>杨广恒</t>
+          <t>杨梦云</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
@@ -1118,11 +1118,11 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>杨梦云</t>
+          <t>马天奇</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
@@ -1167,11 +1167,11 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>马天奇</t>
+          <t>姚梦雨</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
@@ -1216,11 +1216,11 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>姚梦雨</t>
+          <t>侯建文</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
@@ -1265,11 +1265,11 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>侯建文</t>
+          <t>张猛威</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
@@ -1314,11 +1314,11 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>张猛威</t>
+          <t>范文彬</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
@@ -1363,11 +1363,11 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>范文彬</t>
+          <t>王璐瑶</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
@@ -1412,11 +1412,11 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>王璐瑶</t>
+          <t>孙梦圆</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
@@ -1461,11 +1461,11 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>孙梦圆</t>
+          <t>吴沂真</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
@@ -1510,11 +1510,11 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>吴沂真</t>
+          <t>文晓磊</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
@@ -1559,11 +1559,11 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>文晓磊</t>
+          <t>黄梦恩</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
@@ -1608,11 +1608,11 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>黄梦恩</t>
+          <t>张宜成</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
@@ -1657,11 +1657,11 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>张宜成</t>
+          <t>张晨</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
@@ -1706,11 +1706,11 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>张晨</t>
+          <t>戴立伟</t>
         </is>
       </c>
       <c r="C27" s="6" t="n">
@@ -1755,11 +1755,11 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>戴立伟</t>
+          <t>李凡</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
@@ -1804,11 +1804,11 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>李凡</t>
+          <t>陈强</t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
@@ -1853,11 +1853,11 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>陈强</t>
+          <t>李新康</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
@@ -1902,11 +1902,11 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>李新康</t>
+          <t>高宏伟</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
@@ -1951,11 +1951,11 @@
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>高宏伟</t>
+          <t>付嘉豪</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
@@ -2000,11 +2000,11 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>付嘉豪</t>
+          <t>王鸿飞</t>
         </is>
       </c>
       <c r="C33" s="6" t="n">
@@ -2049,11 +2049,11 @@
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>王鸿飞</t>
+          <t>任利程</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
@@ -2098,11 +2098,11 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>任利程</t>
+          <t>姚琦钢</t>
         </is>
       </c>
       <c r="C35" s="6" t="n">
@@ -2147,11 +2147,11 @@
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>姚琦钢</t>
+          <t>林晓雅</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
@@ -2196,11 +2196,11 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>林晓雅</t>
+          <t>孙世纪</t>
         </is>
       </c>
       <c r="C37" s="6" t="n">
@@ -2245,11 +2245,11 @@
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>孙世纪</t>
+          <t>吕梦怡</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
@@ -2294,11 +2294,11 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>吕梦怡</t>
+          <t>易忠延</t>
         </is>
       </c>
       <c r="C39" s="6" t="n">
@@ -2343,11 +2343,11 @@
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>易忠延</t>
+          <t>马静</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
@@ -2392,11 +2392,11 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>马静</t>
+          <t>孙家昌</t>
         </is>
       </c>
       <c r="C41" s="6" t="n">
@@ -2441,11 +2441,11 @@
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>孙家昌</t>
+          <t>孔维泉</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
@@ -2490,11 +2490,11 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>孔维泉</t>
+          <t>臧千蓓</t>
         </is>
       </c>
       <c r="C43" s="6" t="n">
@@ -2539,11 +2539,11 @@
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>臧千蓓</t>
+          <t>吕雅轩</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
@@ -2588,11 +2588,11 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>吕雅轩</t>
+          <t>郭晓明</t>
         </is>
       </c>
       <c r="C45" s="6" t="n">
@@ -2636,74 +2636,25 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>郭晓明</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B47" s="8" t="n"/>
-      <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="n"/>
-      <c r="E47" s="8" t="n"/>
-      <c r="F47" s="8" t="n"/>
-      <c r="G47" s="8" t="n"/>
-      <c r="H47" s="8" t="n"/>
-      <c r="I47" s="8" t="n"/>
-      <c r="J47" s="8" t="n"/>
-      <c r="K47" s="8" t="n"/>
-      <c r="L47" s="8" t="n"/>
-      <c r="M47" s="8" t="n"/>
-      <c r="N47" s="8" t="n"/>
-      <c r="O47" s="3" t="n">
+      <c r="B46" s="8" t="n"/>
+      <c r="C46" s="8" t="n"/>
+      <c r="D46" s="8" t="n"/>
+      <c r="E46" s="8" t="n"/>
+      <c r="F46" s="8" t="n"/>
+      <c r="G46" s="8" t="n"/>
+      <c r="H46" s="8" t="n"/>
+      <c r="I46" s="8" t="n"/>
+      <c r="J46" s="8" t="n"/>
+      <c r="K46" s="8" t="n"/>
+      <c r="L46" s="8" t="n"/>
+      <c r="M46" s="8" t="n"/>
+      <c r="N46" s="8" t="n"/>
+      <c r="O46" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2712,7 +2663,7 @@
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="C2:F2"/>
     <mergeCell ref="G2:N2"/>
-    <mergeCell ref="A47:N47"/>
+    <mergeCell ref="A46:N46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
